--- a/informed_consent_forms/014_e_visits_informed_consent_form--informed_consent_forms.xlsx
+++ b/informed_consent_forms/014_e_visits_informed_consent_form--informed_consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,23 +515,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>e_visits_informed_consent_form</t>
+          <t>e_visits_informed_consent_form_page_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>e_visits_informed_consent_form</t>
+          <t>Informed Consent Overview</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,81 +543,81 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>e_visits_informed_consent_form_2</t>
+          <t>e_visits_informed_consent_form_page_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>e_visits_informed_consent</t>
+          <t>Benefits of E-Visits</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>e_visits_informed_consent_form_3</t>
+          <t>e_visits_informed_consent_form_page_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>e-visits</t>
+          <t>Risks of E-Visits</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>e_visits_informed_consent_form_4</t>
+          <t>e_visits_informed_consent_form_page_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>what-is-e-visits</t>
+          <t>E Visits Schedule</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>e_visits_informed_consent_form_5</t>
+          <t>e_visits_informed_consent_form_page_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>what-are-the-benefits-of-e-visits</t>
+          <t>Frequency of E Visits</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,35 +635,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>e_visits_informed_consent_form_6</t>
+          <t>e_visits_informed_consent_form_page_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>what-are-the-risks-of-e-visits</t>
+          <t>Contact Information</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>e_visits_informed_consent_form_7</t>
+          <t>e_visits_informed_consent_form_page_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>e-visits</t>
+          <t>Consent for E Visits</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>e_visits_informed_consent_form_8</t>
+          <t>e_visits_informed_consent_form_page_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>e-visits</t>
+          <t>Consent for Data Sharing</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,23 +699,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>e_visits_informed_consent_form_9</t>
+          <t>e_visits_informed_consent_form_page_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>e-visits</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,18 +727,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>e_visits_informed_consent_form_10</t>
+          <t>e_visits_informed_consent_form_page_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>e-visits-informed-consent-form-10</t>
+          <t>Date of Birth</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,35 +750,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>e_visits_informed_consent_form_11</t>
+          <t>e_visits_informed_consent_form_page_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>e-visits-informed-consent-form-11</t>
+          <t>Time of Availability</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>e_visits_informed_consent_form_12</t>
+          <t>e_visits_informed_consent_form_page_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>e-visits-informed-consent-form-12</t>
+          <t>Additional Information</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,69 +791,69 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>e_visits_informed_consent_form_13</t>
+          <t>e_visits_informed_consent_form_page_13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>e-visits-informed-consent-form-13</t>
+          <t>Schedule for Follow-Up E Visits</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>e_visits_informed_consent_form_14</t>
+          <t>e_visits_informed_consent_form_page_14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>e-visits-informed-consent-form-14</t>
+          <t>Time for Follow-Up E Visits</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>e_visits_informed_consent_form_15</t>
+          <t>e_visits_informed_consent_form_page_15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>e-visits-informed-consent-form-15</t>
+          <t>Review and Agreement</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="47" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -896,136 +896,119 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>e_visits_informed_consent_form_3_choices</t>
+          <t>e_visits_informed_consent_form_page_5_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>once</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Once</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>e_visits_informed_consent_form_3_choices</t>
+          <t>e_visits_informed_consent_form_page_5_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>e_visits_informed_consent_form_7_choices</t>
+          <t>e_visits_informed_consent_form_page_5_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>e_visits_informed_consent_form_7_choices</t>
+          <t>e_visits_informed_consent_form_page_7_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>e_visits_informed_consent_form_8_choices</t>
+          <t>e_visits_informed_consent_form_page_7_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>e_visits_informed_consent_form_8_choices</t>
+          <t>e_visits_informed_consent_form_page_8_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>e_visits_informed_consent_form_9_choices</t>
+          <t>e_visits_informed_consent_form_page_8_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>e_visits_informed_consent_form_9_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
